--- a/examples/HFP_helen+ruth.xlsx
+++ b/examples/HFP_helen+ruth.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,60 +432,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>gross earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -525,10 +535,17 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -566,10 +583,17 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -607,10 +631,17 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -648,10 +679,17 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -689,10 +727,17 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -730,10 +775,17 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -771,10 +823,17 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -812,10 +871,17 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -853,10 +919,17 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -894,10 +967,17 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -935,10 +1015,17 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -976,10 +1063,17 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1017,10 +1111,17 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1058,10 +1159,17 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1099,10 +1207,17 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1140,10 +1255,17 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1181,10 +1303,17 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1222,10 +1351,17 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1263,10 +1399,17 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1304,10 +1447,17 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1345,10 +1495,17 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1386,10 +1543,17 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1427,10 +1591,17 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1468,10 +1639,17 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1509,10 +1687,17 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1550,10 +1735,17 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1591,10 +1783,17 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1632,10 +1831,17 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1673,10 +1879,17 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1714,10 +1927,17 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1755,10 +1975,17 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1796,10 +2023,17 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1837,10 +2071,17 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1878,10 +2119,17 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1919,10 +2167,17 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1960,10 +2215,17 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2001,10 +2263,17 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2042,10 +2311,17 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2083,10 +2359,17 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2124,10 +2407,17 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2142,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,60 +2448,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>gross earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -2251,10 +2551,17 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2292,10 +2599,17 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2333,10 +2647,17 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2374,10 +2695,17 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2415,10 +2743,17 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2456,10 +2791,17 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2497,10 +2839,17 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2538,10 +2887,17 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2579,10 +2935,17 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2620,10 +2983,17 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2661,10 +3031,17 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2702,10 +3079,17 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2743,10 +3127,17 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2784,10 +3175,17 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2825,10 +3223,17 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2866,10 +3271,17 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2907,10 +3319,17 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2948,10 +3367,17 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2989,10 +3415,17 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3030,10 +3463,17 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3071,10 +3511,17 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3112,10 +3559,17 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3153,10 +3607,17 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3194,10 +3655,17 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3235,10 +3703,17 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3276,10 +3751,17 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3317,10 +3799,17 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3358,10 +3847,17 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3399,10 +3895,17 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3440,10 +3943,17 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3481,10 +3991,17 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3522,10 +4039,17 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3563,10 +4087,17 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3604,10 +4135,17 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3645,10 +4183,17 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3686,10 +4231,17 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3727,10 +4279,17 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3768,10 +4327,17 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3809,10 +4375,17 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3850,10 +4423,17 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3870,10 +4450,6 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/examples/HFP_helen+ruth.xlsx
+++ b/examples/HFP_helen+ruth.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,70 +432,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gross earnings</t>
+          <t>other inc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>months worked</t>
+          <t>net inv</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>other inc</t>
+          <t>taxable ctrb</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>net inv</t>
+          <t>401k ctrb</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>taxable ctrb</t>
+          <t>Roth 401k ctrb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>401k ctrb</t>
+          <t>IRA ctrb</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Roth 401k ctrb</t>
+          <t>Roth IRA ctrb</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>IRA ctrb</t>
+          <t>HSA ctrb</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Roth IRA ctrb</t>
+          <t>Roth conv</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>HSA ctrb</t>
+          <t>Roth conv fixed</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Roth conv</t>
+          <t>QCD</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>Roth conv fixed</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>QCD</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -535,17 +525,10 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -583,17 +566,10 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -631,17 +607,10 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -679,17 +648,10 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -727,17 +689,10 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -775,17 +730,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -823,17 +771,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -871,17 +812,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -919,17 +853,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -967,17 +894,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1015,17 +935,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1063,17 +976,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1111,17 +1017,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1159,17 +1058,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1207,17 +1099,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1255,17 +1140,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1303,17 +1181,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1351,17 +1222,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1399,17 +1263,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1447,17 +1304,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1495,17 +1345,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1543,17 +1386,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1591,17 +1427,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1639,17 +1468,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1687,17 +1509,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1735,17 +1550,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1783,17 +1591,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1831,17 +1632,10 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1879,17 +1673,10 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1927,17 +1714,10 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1975,17 +1755,10 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2023,17 +1796,10 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2071,17 +1837,10 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2119,17 +1878,10 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2167,17 +1919,10 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2215,17 +1960,10 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2263,17 +2001,10 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2311,17 +2042,10 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
+      <c r="N39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2359,17 +2083,10 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="N40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2407,17 +2124,10 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
+      <c r="N41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2432,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2448,70 +2158,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gross earnings</t>
+          <t>other inc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>months worked</t>
+          <t>net inv</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>other inc</t>
+          <t>taxable ctrb</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>net inv</t>
+          <t>401k ctrb</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>taxable ctrb</t>
+          <t>Roth 401k ctrb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>401k ctrb</t>
+          <t>IRA ctrb</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Roth 401k ctrb</t>
+          <t>Roth IRA ctrb</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>IRA ctrb</t>
+          <t>HSA ctrb</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Roth IRA ctrb</t>
+          <t>Roth conv</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>HSA ctrb</t>
+          <t>Roth conv fixed</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Roth conv</t>
+          <t>QCD</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>Roth conv fixed</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>QCD</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -2551,17 +2251,10 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2599,17 +2292,10 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2647,17 +2333,10 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2695,17 +2374,10 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2743,17 +2415,10 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2791,17 +2456,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2839,17 +2497,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2887,17 +2538,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2935,17 +2579,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2983,17 +2620,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3031,17 +2661,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3079,17 +2702,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3127,17 +2743,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3175,17 +2784,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3223,17 +2825,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3271,17 +2866,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3319,17 +2907,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3367,17 +2948,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3415,17 +2989,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3463,17 +3030,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3511,17 +3071,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3559,17 +3112,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3607,17 +3153,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3655,17 +3194,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3703,17 +3235,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3751,17 +3276,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3799,17 +3317,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3847,17 +3358,10 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3895,17 +3399,10 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3943,17 +3440,10 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3991,17 +3481,10 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4039,17 +3522,10 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4087,17 +3563,10 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4135,17 +3604,10 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4183,17 +3645,10 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4231,17 +3686,10 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4279,17 +3727,10 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4327,17 +3768,10 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
+      <c r="N39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4375,17 +3809,10 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="N40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4423,17 +3850,10 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
+      <c r="N41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4450,6 +3870,10 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
